--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_ch_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_ch_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>17-05-2021 08:30</t>
+          <t>2021-05-17 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>09-07-2021 08:30</t>
+          <t>2021-09-07 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
